--- a/ksoft_old/docs/records/Cost_Center_Records.xlsx
+++ b/ksoft_old/docs/records/Cost_Center_Records.xlsx
@@ -3581,13 +3581,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6F46373-B018-4BBA-8A7C-1E2FD26E2E42}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93DBEEDD-DA3C-402A-9AF3-74C6D5BB397B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDC39F45-A923-4B7A-9219-62FBF99ADA10}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E15F3B61-5E98-4BE4-89EF-5EEEB27097B1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B2A7172-1D68-4963-9256-AC0ACDF3521A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796A17AA-2480-4D14-9698-E4F7B5FC23A7}"/>
 </file>
--- a/ksoft_old/docs/records/Cost_Center_Records.xlsx
+++ b/ksoft_old/docs/records/Cost_Center_Records.xlsx
@@ -3581,13 +3581,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93DBEEDD-DA3C-402A-9AF3-74C6D5BB397B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{946E50DA-7465-4C26-B98A-4F685A41AA4E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E15F3B61-5E98-4BE4-89EF-5EEEB27097B1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154FEA07-FA58-4468-820B-C45890728CFF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{796A17AA-2480-4D14-9698-E4F7B5FC23A7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14B38608-CA42-47A3-AE7D-BAA98886ADEA}"/>
 </file>
--- a/ksoft_old/docs/records/Cost_Center_Records.xlsx
+++ b/ksoft_old/docs/records/Cost_Center_Records.xlsx
@@ -3581,13 +3581,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{946E50DA-7465-4C26-B98A-4F685A41AA4E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6F46373-B018-4BBA-8A7C-1E2FD26E2E42}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154FEA07-FA58-4468-820B-C45890728CFF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDC39F45-A923-4B7A-9219-62FBF99ADA10}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14B38608-CA42-47A3-AE7D-BAA98886ADEA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B2A7172-1D68-4963-9256-AC0ACDF3521A}"/>
 </file>